--- a/assets/docs/lop5/Lich su va Dia li - Lop 5.xlsx
+++ b/assets/docs/lop5/Lich su va Dia li - Lop 5.xlsx
@@ -1077,19 +1077,19 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Ôn tập, kiểm tra, đánh giá</t>
+          <t>Chủ đề 3: Xây dựng và bảo vệ đất nước Việt Nam</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr"/>
       <c r="D21" s="4" t="inlineStr"/>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>Kiểm tra định kì giữa học kì I</t>
+          <t>Bài 8. Đấu tranh giành độc lập thời kì Bắc thuộc (Tiết 1)</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>1 tiết</t>
+          <t>2 tiết</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
@@ -1097,7 +1097,12 @@
           <t>18</t>
         </is>
       </c>
-      <c r="H21" s="4" t="inlineStr"/>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số 1.1 CB2c: HS tham quan bảo tàng số, quan sát hiện vật ở nhiều góc.
+KNS: KN ứng phó với thiên tai thường gặp ở địa phương.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -1114,14 +1119,10 @@
       <c r="D22" s="4" t="inlineStr"/>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>Bài 8. Đấu tranh giành độc lập thời kì Bắc thuộc (Tiết 1)</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>2 tiết</t>
-        </is>
-      </c>
+          <t>Bài 8. Đấu tranh giành độc lập thời kì Bắc thuộc (Tiết 2)</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr"/>
       <c r="G22" s="4" t="inlineStr">
         <is>
           <t>19</t>
@@ -1129,8 +1130,7 @@
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB2c: HS tham quan bảo tàng số, quan sát hiện vật ở nhiều góc.
-KNS: KN ứng phó với thiên tai thường gặp ở địa phương.</t>
+          <t>Năng lực số 1.1 CB2c: HS tham quan bảo tàng số, quan sát hiện vật ở nhiều góc.</t>
         </is>
       </c>
     </row>
@@ -1149,10 +1149,14 @@
       <c r="D23" s="4" t="inlineStr"/>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>Bài 8. Đấu tranh giành độc lập thời kì Bắc thuộc (Tiết 2)</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr"/>
+          <t>Bài 9. Triều Lý và việc định đô ở Thăng Long (Tiết 1)</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>3 tiết</t>
+        </is>
+      </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
           <t>20</t>
@@ -1160,7 +1164,8 @@
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB2c: HS tham quan bảo tàng số, quan sát hiện vật ở nhiều góc.</t>
+          <t>Năng lực số 1.1 CB2c: HS tham quan bảo tàng số, quan sát hiện vật ở nhiều góc.
+QPAN: Giáo dục truyền thống dựng nước và giữ nước, tinh thần chống giặc ngoại xâm của dân tộc; bồi dưỡng niềm tự hào dân tộc và lòng biết ơn các anh hùng, liệt sĩ đã hi sinh bảo vệ Tổ quốc.</t>
         </is>
       </c>
     </row>
@@ -1179,14 +1184,10 @@
       <c r="D24" s="4" t="inlineStr"/>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>Bài 9. Triều Lý và việc định đô ở Thăng Long (Tiết 1)</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>3 tiết</t>
-        </is>
-      </c>
+          <t>Bài 9. Triều Lý và việc định đô ở Thăng Long (Tiết 2)</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr"/>
       <c r="G24" s="4" t="inlineStr">
         <is>
           <t>21</t>
@@ -1194,8 +1195,7 @@
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB2c: HS tham quan bảo tàng số, quan sát hiện vật ở nhiều góc.
-QPAN: Giáo dục truyền thống dựng nước và giữ nước, tinh thần chống giặc ngoại xâm của dân tộc; bồi dưỡng niềm tự hào dân tộc và lòng biết ơn các anh hùng, liệt sĩ đã hi sinh bảo vệ Tổ quốc.</t>
+          <t>Năng lực số 1.1 CB2c: HS tham quan bảo tàng số, quan sát hiện vật ở nhiều góc.</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
       <c r="D25" s="4" t="inlineStr"/>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>Bài 9. Triều Lý và việc định đô ở Thăng Long (Tiết 2)</t>
+          <t>Bài 9. Triều Lý và việc định đô ở Thăng Long (Tiết 3)</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr"/>
@@ -1223,11 +1223,7 @@
           <t>22</t>
         </is>
       </c>
-      <c r="H25" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 1.1 CB2c: HS tham quan bảo tàng số, quan sát hiện vật ở nhiều góc.</t>
-        </is>
-      </c>
+      <c r="H25" s="4" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
@@ -1244,16 +1240,26 @@
       <c r="D26" s="4" t="inlineStr"/>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>Bài 9. Triều Lý và việc định đô ở Thăng Long (Tiết 3)</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="inlineStr"/>
+          <t>Bài 10. Triều Trần xây dựng đất nước và kháng chiến chống quân Mông – Nguyên xâm lược (Tiết 1)</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>4 tiết</t>
+        </is>
+      </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="H26" s="4" t="inlineStr"/>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>- Nội dung 1, câu chuyện lịch sử: địa điểm Ninh Bình - Trang 46, câu chuyện lịch sử: Địa điểm Chí Linh (Hải Phòng)
+Năng lực số 1.1 CB2c: HS tham quan bảo tàng số, quan sát hiện vật ở nhiều góc.
+QPAN: Giáo dục truyền thống dựng nước và giữ nước, tinh thần chống giặc ngoại xâm của dân tộc; bồi dưỡng niềm tự hào dân tộc và lòng biết ơn các anh hùng, liệt sĩ đã hi sinh bảo vệ Tổ quốc.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -1270,14 +1276,10 @@
       <c r="D27" s="4" t="inlineStr"/>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>Bài 10. Triều Trần xây dựng đất nước và kháng chiến chống quân Mông – Nguyên xâm lược (Tiết 1)</t>
-        </is>
-      </c>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>4 tiết</t>
-        </is>
-      </c>
+          <t>Bài 10. Triều Trần xây dựng đất nước và kháng chiến chống quân Mông – Nguyên xâm lược (Tiết 2)</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr"/>
       <c r="G27" s="4" t="inlineStr">
         <is>
           <t>24</t>
@@ -1285,9 +1287,7 @@
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>- Nội dung 1, câu chuyện lịch sử: địa điểm Ninh Bình - Trang 46, câu chuyện lịch sử: Địa điểm Chí Linh (Hải Phòng)
-Năng lực số 1.1 CB2c: HS tham quan bảo tàng số, quan sát hiện vật ở nhiều góc.
-QPAN: Giáo dục truyền thống dựng nước và giữ nước, tinh thần chống giặc ngoại xâm của dân tộc; bồi dưỡng niềm tự hào dân tộc và lòng biết ơn các anh hùng, liệt sĩ đã hi sinh bảo vệ Tổ quốc.</t>
+          <t>Năng lực số 1.1 CB2c: HS tham quan bảo tàng số, quan sát hiện vật ở nhiều góc.</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
       <c r="D28" s="4" t="inlineStr"/>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>Bài 10. Triều Trần xây dựng đất nước và kháng chiến chống quân Mông – Nguyên xâm lược (Tiết 2)</t>
+          <t>Bài 10. Triều Trần xây dựng đất nước và kháng chiến chống quân Mông – Nguyên xâm lược (Tiết 3)</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr"/>
@@ -1315,11 +1315,7 @@
           <t>25</t>
         </is>
       </c>
-      <c r="H28" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 1.1 CB2c: HS tham quan bảo tàng số, quan sát hiện vật ở nhiều góc.</t>
-        </is>
-      </c>
+      <c r="H28" s="4" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
@@ -1336,7 +1332,7 @@
       <c r="D29" s="4" t="inlineStr"/>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>Bài 10. Triều Trần xây dựng đất nước và kháng chiến chống quân Mông – Nguyên xâm lược (Tiết 3)</t>
+          <t>Bài 10. Triều Trần xây dựng đất nước và kháng chiến chống quân Mông – Nguyên xâm lược (Tiết 4)</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr"/>
@@ -1362,10 +1358,14 @@
       <c r="D30" s="4" t="inlineStr"/>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>Bài 10. Triều Trần xây dựng đất nước và kháng chiến chống quân Mông – Nguyên xâm lược (Tiết 4)</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="inlineStr"/>
+          <t>Bài 11. Ôn tập (Tiết 1)</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>2 tiết</t>
+        </is>
+      </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
           <t>27</t>
@@ -1388,24 +1388,16 @@
       <c r="D31" s="4" t="inlineStr"/>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>Bài 11. Ôn tập</t>
-        </is>
-      </c>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>1 tiết</t>
-        </is>
-      </c>
+          <t>Bài 11. Ôn tập (Tiết 2)</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr"/>
       <c r="G31" s="4" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="H31" s="4" t="inlineStr">
-        <is>
-          <t>SGV 2 tiết; bớt 1 tiết cho kiểm tra định kì</t>
-        </is>
-      </c>
+      <c r="H31" s="4" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
@@ -2152,19 +2144,19 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Ôn tập, kiểm tra, đánh giá</t>
+          <t>Chủ đề 5: Tìm hiểu thế giới</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr"/>
       <c r="D55" s="4" t="inlineStr"/>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>Kiểm tra định kì giữa học kì II</t>
+          <t>Bài 22. Các châu lục và đại dương trên thế giới (Tiết 1)</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>1 tiết</t>
+          <t>5 tiết</t>
         </is>
       </c>
       <c r="G55" s="4" t="inlineStr">
@@ -2172,7 +2164,12 @@
           <t>52</t>
         </is>
       </c>
-      <c r="H55" s="4" t="inlineStr"/>
+      <c r="H55" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số 1.1 CB2c: HS thao tác bản đồ, quả địa cầu số.
+KNS: KN ứng phó với thiên tai thường gặp ở địa phương.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
@@ -2189,14 +2186,10 @@
       <c r="D56" s="4" t="inlineStr"/>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>Bài 22. Các châu lục và đại dương trên thế giới (Tiết 1)</t>
-        </is>
-      </c>
-      <c r="F56" s="4" t="inlineStr">
-        <is>
-          <t>5 tiết</t>
-        </is>
-      </c>
+          <t>Bài 22. Các châu lục và đại dương trên thế giới (Tiết 2)</t>
+        </is>
+      </c>
+      <c r="F56" s="4" t="inlineStr"/>
       <c r="G56" s="4" t="inlineStr">
         <is>
           <t>53</t>
@@ -2204,8 +2197,7 @@
       </c>
       <c r="H56" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB2c: HS thao tác bản đồ, quả địa cầu số.
-KNS: KN ứng phó với thiên tai thường gặp ở địa phương.</t>
+          <t>Năng lực số 1.1 CB2c: HS thao tác bản đồ, quả địa cầu số.</t>
         </is>
       </c>
     </row>
@@ -2224,7 +2216,7 @@
       <c r="D57" s="4" t="inlineStr"/>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>Bài 22. Các châu lục và đại dương trên thế giới (Tiết 2)</t>
+          <t>Bài 22. Các châu lục và đại dương trên thế giới (Tiết 3)</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr"/>
@@ -2233,11 +2225,7 @@
           <t>54</t>
         </is>
       </c>
-      <c r="H57" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 1.1 CB2c: HS thao tác bản đồ, quả địa cầu số.</t>
-        </is>
-      </c>
+      <c r="H57" s="4" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
@@ -2254,7 +2242,7 @@
       <c r="D58" s="4" t="inlineStr"/>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>Bài 22. Các châu lục và đại dương trên thế giới (Tiết 3)</t>
+          <t>Bài 22. Các châu lục và đại dương trên thế giới (Tiết 4)</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr"/>
@@ -2280,7 +2268,7 @@
       <c r="D59" s="4" t="inlineStr"/>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>Bài 22. Các châu lục và đại dương trên thế giới (Tiết 4)</t>
+          <t>Bài 22. Các châu lục và đại dương trên thế giới (Tiết 5)</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr"/>
@@ -2306,16 +2294,24 @@
       <c r="D60" s="4" t="inlineStr"/>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>Bài 22. Các châu lục và đại dương trên thế giới (Tiết 5)</t>
-        </is>
-      </c>
-      <c r="F60" s="4" t="inlineStr"/>
+          <t>Bài 23. Dân số và các chủng tộc chính trên thế giới (Tiết 1)</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t>2 tiết</t>
+        </is>
+      </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
           <t>57</t>
         </is>
       </c>
-      <c r="H60" s="4" t="inlineStr"/>
+      <c r="H60" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số 1.1 CB2c: HS thao tác bản đồ, quả địa cầu số.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
@@ -2332,14 +2328,10 @@
       <c r="D61" s="4" t="inlineStr"/>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>Bài 23. Dân số và các chủng tộc chính trên thế giới (Tiết 1)</t>
-        </is>
-      </c>
-      <c r="F61" s="4" t="inlineStr">
-        <is>
-          <t>2 tiết</t>
-        </is>
-      </c>
+          <t>Bài 23. Dân số và các chủng tộc chính trên thế giới (Tiết 2)</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="inlineStr"/>
       <c r="G61" s="4" t="inlineStr">
         <is>
           <t>58</t>
@@ -2366,10 +2358,14 @@
       <c r="D62" s="4" t="inlineStr"/>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>Bài 23. Dân số và các chủng tộc chính trên thế giới (Tiết 2)</t>
-        </is>
-      </c>
-      <c r="F62" s="4" t="inlineStr"/>
+          <t>Bài 24. Văn minh Ai Cập (Tiết 1)</t>
+        </is>
+      </c>
+      <c r="F62" s="4" t="inlineStr">
+        <is>
+          <t>2 tiết</t>
+        </is>
+      </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
           <t>59</t>
@@ -2377,7 +2373,7 @@
       </c>
       <c r="H62" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB2c: HS thao tác bản đồ, quả địa cầu số.</t>
+          <t>Năng lực số 1.1 CB2c: HS tham quan bảo tàng số, quan sát hiện vật ở nhiều góc.</t>
         </is>
       </c>
     </row>
@@ -2396,14 +2392,10 @@
       <c r="D63" s="4" t="inlineStr"/>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>Bài 24. Văn minh Ai Cập (Tiết 1)</t>
-        </is>
-      </c>
-      <c r="F63" s="4" t="inlineStr">
-        <is>
-          <t>2 tiết</t>
-        </is>
-      </c>
+          <t>Bài 24. Văn minh Ai Cập (Tiết 2)</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="inlineStr"/>
       <c r="G63" s="4" t="inlineStr">
         <is>
           <t>60</t>
@@ -2430,10 +2422,14 @@
       <c r="D64" s="4" t="inlineStr"/>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>Bài 24. Văn minh Ai Cập (Tiết 2)</t>
-        </is>
-      </c>
-      <c r="F64" s="4" t="inlineStr"/>
+          <t>Bài 25. Văn minh Hy Lạp (Tiết 1)</t>
+        </is>
+      </c>
+      <c r="F64" s="4" t="inlineStr">
+        <is>
+          <t>2 tiết</t>
+        </is>
+      </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
           <t>61</t>
@@ -2460,14 +2456,10 @@
       <c r="D65" s="4" t="inlineStr"/>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>Bài 25. Văn minh Hy Lạp (Tiết 1)</t>
-        </is>
-      </c>
-      <c r="F65" s="4" t="inlineStr">
-        <is>
-          <t>2 tiết</t>
-        </is>
-      </c>
+          <t>Bài 25. Văn minh Hy Lạp (Tiết 2)</t>
+        </is>
+      </c>
+      <c r="F65" s="4" t="inlineStr"/>
       <c r="G65" s="4" t="inlineStr">
         <is>
           <t>62</t>
@@ -2487,17 +2479,21 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 5: Tìm hiểu thế giới</t>
+          <t>Chủ đề 6: Chung tay xây dựng thế giới</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr"/>
       <c r="D66" s="4" t="inlineStr"/>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>Bài 25. Văn minh Hy Lạp (Tiết 2)</t>
-        </is>
-      </c>
-      <c r="F66" s="4" t="inlineStr"/>
+          <t>Bài 26. Xây dựng thế giới xanh – sạch – đẹp (Tiết 1)</t>
+        </is>
+      </c>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t>2 tiết</t>
+        </is>
+      </c>
       <c r="G66" s="4" t="inlineStr">
         <is>
           <t>63</t>
@@ -2505,7 +2501,8 @@
       </c>
       <c r="H66" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB2c: HS tham quan bảo tàng số, quan sát hiện vật ở nhiều góc.</t>
+          <t>-HĐ Khám phá: Một số vấn đề về môi trường. +Hình 2 nhắc đến tỉnh Quảng Nam. *Cập nhật Quảng Nam sáp nhập thành Đà Nẵng; NLS-KT: sử dụng bản đồ số/tranh ảnh/tư liệu số; hướng dẫn HS ghi nguồn thông tin.
+Năng lực số 1.1 CB2c: HS thao tác bản đồ, quả địa cầu số.</t>
         </is>
       </c>
     </row>
@@ -2524,14 +2521,10 @@
       <c r="D67" s="4" t="inlineStr"/>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>Bài 26. Xây dựng thế giới xanh – sạch – đẹp (Tiết 1)</t>
-        </is>
-      </c>
-      <c r="F67" s="4" t="inlineStr">
-        <is>
-          <t>2 tiết</t>
-        </is>
-      </c>
+          <t>Bài 26. Xây dựng thế giới xanh – sạch – đẹp (Tiết 2)</t>
+        </is>
+      </c>
+      <c r="F67" s="4" t="inlineStr"/>
       <c r="G67" s="4" t="inlineStr">
         <is>
           <t>64</t>
@@ -2539,8 +2532,7 @@
       </c>
       <c r="H67" s="4" t="inlineStr">
         <is>
-          <t>-HĐ Khám phá: Một số vấn đề về môi trường. +Hình 2 nhắc đến tỉnh Quảng Nam. *Cập nhật Quảng Nam sáp nhập thành Đà Nẵng; NLS-KT: sử dụng bản đồ số/tranh ảnh/tư liệu số; hướng dẫn HS ghi nguồn thông tin.
-Năng lực số 1.1 CB2c: HS thao tác bản đồ, quả địa cầu số.</t>
+          <t>Năng lực số 1.1 CB2c: HS thao tác bản đồ, quả địa cầu số.</t>
         </is>
       </c>
     </row>
@@ -2559,10 +2551,14 @@
       <c r="D68" s="4" t="inlineStr"/>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>Bài 26. Xây dựng thế giới xanh – sạch – đẹp (Tiết 2)</t>
-        </is>
-      </c>
-      <c r="F68" s="4" t="inlineStr"/>
+          <t>Bài 27. Xây dựng thế giới hoà bình (Tiết 1)</t>
+        </is>
+      </c>
+      <c r="F68" s="4" t="inlineStr">
+        <is>
+          <t>2 tiết</t>
+        </is>
+      </c>
       <c r="G68" s="4" t="inlineStr">
         <is>
           <t>65</t>
@@ -2570,7 +2566,8 @@
       </c>
       <c r="H68" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB2c: HS thao tác bản đồ, quả địa cầu số.</t>
+          <t>Lồng ghép GDQPAN: Yêu hoà bình, bảo vệ hoà bình bằng những việc phù hợp với khả năng, phản đối chiến tranh.
+Năng lực số 1.1 CB2c: HS thao tác bản đồ, quả địa cầu số.</t>
         </is>
       </c>
     </row>
@@ -2589,14 +2586,10 @@
       <c r="D69" s="4" t="inlineStr"/>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>Bài 27. Xây dựng thế giới hoà bình (Tiết 1)</t>
-        </is>
-      </c>
-      <c r="F69" s="4" t="inlineStr">
-        <is>
-          <t>2 tiết</t>
-        </is>
-      </c>
+          <t>Bài 27. Xây dựng thế giới hoà bình (Tiết 2)</t>
+        </is>
+      </c>
+      <c r="F69" s="4" t="inlineStr"/>
       <c r="G69" s="4" t="inlineStr">
         <is>
           <t>66</t>
@@ -2604,8 +2597,7 @@
       </c>
       <c r="H69" s="4" t="inlineStr">
         <is>
-          <t>Lồng ghép GDQPAN: Yêu hoà bình, bảo vệ hoà bình bằng những việc phù hợp với khả năng, phản đối chiến tranh.
-Năng lực số 1.1 CB2c: HS thao tác bản đồ, quả địa cầu số.</t>
+          <t>Năng lực số 1.1 CB2c: HS thao tác bản đồ, quả địa cầu số.</t>
         </is>
       </c>
     </row>
@@ -2624,20 +2616,20 @@
       <c r="D70" s="4" t="inlineStr"/>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>Bài 27. Xây dựng thế giới hoà bình (Tiết 2)</t>
-        </is>
-      </c>
-      <c r="F70" s="4" t="inlineStr"/>
+          <t>Bài 28. Ôn tập (Tiết 1)</t>
+        </is>
+      </c>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t>3 tiết</t>
+        </is>
+      </c>
       <c r="G70" s="4" t="inlineStr">
         <is>
           <t>67</t>
         </is>
       </c>
-      <c r="H70" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 1.1 CB2c: HS thao tác bản đồ, quả địa cầu số.</t>
-        </is>
-      </c>
+      <c r="H70" s="4" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
@@ -2654,24 +2646,16 @@
       <c r="D71" s="4" t="inlineStr"/>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>Bài 28. Ôn tập (Tiết 1)</t>
-        </is>
-      </c>
-      <c r="F71" s="4" t="inlineStr">
-        <is>
-          <t>2 tiết</t>
-        </is>
-      </c>
+          <t>Bài 28. Ôn tập (Tiết 2)</t>
+        </is>
+      </c>
+      <c r="F71" s="4" t="inlineStr"/>
       <c r="G71" s="4" t="inlineStr">
         <is>
           <t>68</t>
         </is>
       </c>
-      <c r="H71" s="4" t="inlineStr">
-        <is>
-          <t>SGV 3 tiết; bớt 1 tiết cho kiểm tra định kì</t>
-        </is>
-      </c>
+      <c r="H71" s="4" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
@@ -2688,7 +2672,7 @@
       <c r="D72" s="4" t="inlineStr"/>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>Bài 28. Ôn tập (Tiết 2)</t>
+          <t>Bài 28. Ôn tập (Tiết 3)</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr"/>
